--- a/output/full_scan/batch_seq7_2026-10-05.xlsx
+++ b/output/full_scan/batch_seq7_2026-10-05.xlsx
@@ -538,7 +538,7 @@
         <v/>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1180.943363229679</v>
+        <v>1380.943363229679</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>133</v>
@@ -552,10 +552,10 @@
         <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>66.20727938391403</v>
+        <v>66.20727938065362</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>27.38927374142375</v>
+        <v>27.38927377289356</v>
       </c>
       <c r="J2" s="2" t="n">
         <v>1.723350424015558</v>
@@ -570,31 +570,31 @@
         <v>-1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.5539070492837379</v>
+        <v>0.5539070493505123</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, obv_uptrend, dealer_buy_3d, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>6651</v>
+        <v>6658</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>全宇昕</t>
+          <t>聯策</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
         <v/>
       </c>
       <c r="D3" s="2" t="n">
-        <v>1032.505084648294</v>
+        <v>1294</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>156</v>
+        <v>200</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
@@ -605,16 +605,16 @@
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>61.85343627628972</v>
+        <v>72.05354924299577</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>18.76226038952558</v>
+        <v>23.8757993066152</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>3.070547087676525</v>
+        <v>5.611465098613972</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L3" s="2" t="n">
         <v>0</v>
@@ -623,31 +623,31 @@
         <v>-1</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.2420706487807042</v>
+        <v>1.90222971802299</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, hist_turn_positive, foreign_buy_3d, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>6658</v>
+        <v>6691</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>聯策</t>
+          <t>洋基工程</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
         <v/>
       </c>
       <c r="D4" s="2" t="n">
-        <v>929</v>
+        <v>1203.311599108062</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>200</v>
+        <v>794</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -658,49 +658,49 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>72.05354926099513</v>
+        <v>76.04531949327877</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>23.87579929052745</v>
+        <v>26.95864247464353</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>5.611465098613972</v>
+        <v>2.431159910806242</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M4" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>1.902229717822721</v>
+        <v>19.14377176187537</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>6548</v>
+        <v>6651</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>長科*</t>
+          <t>全宇昕</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
         <v/>
       </c>
       <c r="D5" s="2" t="n">
-        <v>921.1949124577192</v>
+        <v>1147.505084648294</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>78</v>
+        <v>156</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -711,49 +711,49 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>62.26722628108618</v>
+        <v>61.85343628053777</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>15.57629824533507</v>
+        <v>18.76226037482358</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>3.040043443033319</v>
+        <v>3.070547087676525</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M5" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.5278708366762912</v>
+        <v>0.242070648847458</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, invest_trust_buy_2d, dealer_buy_3d, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
+          <t>macd_golden_cross, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, hist_turn_positive, foreign_buy_3d, stronger_than_market, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>6708</v>
+        <v>6531</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>天擎</t>
+          <t>愛普*</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
         <v/>
       </c>
       <c r="D6" s="2" t="n">
-        <v>884.5559222994942</v>
+        <v>1121.530745856465</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>68.59999999999999</v>
+        <v>1055</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -764,49 +764,49 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>79.44363605627419</v>
+        <v>61.30024243523077</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>20.36940608717189</v>
+        <v>12.00446551962663</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>2.555592229949426</v>
+        <v>1.398558772794182</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M6" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>2.927787203801312</v>
+        <v>4.160942072716079</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, foreign_buy_3d, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, hist_turn_positive, stronger_than_market, obv_uptrend, invest_trust_buy_2d, bb_squeeze_breakout, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>6531</v>
+        <v>6548</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>愛普*</t>
+          <t>長科*</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
         <v/>
       </c>
       <c r="D7" s="2" t="n">
-        <v>866.5307458564639</v>
+        <v>1091.194912457719</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1055</v>
+        <v>78</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -817,49 +817,49 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>61.3002424432995</v>
+        <v>62.26722629013632</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>12.0044655475025</v>
+        <v>15.57629827002744</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>1.398558772794182</v>
+        <v>3.040043443033319</v>
       </c>
       <c r="K7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M7" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>4.160942072270967</v>
+        <v>0.5278708366317788</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, hist_turn_positive, obv_uptrend, bb_squeeze_breakout, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, invest_trust_buy_2d, dealer_buy_3d, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>6664</v>
+        <v>6672</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>群翊</t>
+          <t>騰輝電子-KY</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
         <v/>
       </c>
       <c r="D8" s="2" t="n">
-        <v>827.9337944579004</v>
+        <v>985.1500409606624</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>385</v>
+        <v>451</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -870,49 +870,49 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>66.6901904708098</v>
+        <v>84.30540007784967</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>18.12854236230468</v>
+        <v>39.83217921492995</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>2.543371942297095</v>
+        <v>1.61500409606623</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M8" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>4.836704947403732</v>
+        <v>14.62304173764725</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, invest_trust_buy_2d, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>6691</v>
+        <v>6664</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>洋基工程</t>
+          <t>群翊</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>788.3115991080624</v>
+        <v>967.9337944578988</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>794</v>
+        <v>385</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -923,49 +923,49 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>76.04531945488013</v>
+        <v>66.6901904650596</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>26.9586425003696</v>
+        <v>18.12854240105699</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>2.431159910806242</v>
+        <v>2.543371942297095</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M9" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>19.14377176109648</v>
+        <v>4.83670494695863</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, invest_trust_buy_2d, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>6672</v>
+        <v>6742</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>騰輝電子-KY</t>
+          <t>澤米</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>785.1500409606623</v>
+        <v>920.5323674271468</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>451</v>
+        <v>60.2</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -976,16 +976,16 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>84.30540007532682</v>
+        <v>74.01853830711191</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>39.8321792015691</v>
+        <v>49.06471084444188</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>1.61500409606623</v>
+        <v>2.153236742714691</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L10" s="2" t="n">
         <v>0</v>
@@ -994,31 +994,31 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>14.62304173755827</v>
+        <v>0.9330729052063278</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>6805</v>
+        <v>6525</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>捷敏-KY</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>748.5561917154168</v>
+        <v>903.1601895520506</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>2450</v>
+        <v>140</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1029,13 +1029,13 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>59.23059788467629</v>
+        <v>57.24072542512223</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>35.10981645292655</v>
+        <v>13.17901670905793</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>1.735996901127361</v>
+        <v>2.827913531966264</v>
       </c>
       <c r="K11" s="2" t="n">
         <v>0</v>
@@ -1047,31 +1047,31 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>-8.594831510740704</v>
+        <v>1.471029358911697</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, dealer_buy_3d, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>6811</v>
+        <v>6505</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>宏碁資訊</t>
+          <t>台塑化</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>739.9866181586093</v>
+        <v>884.9014034948467</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>246.5</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1082,49 +1082,49 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>55.75132730342512</v>
+        <v>69.64682784002696</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>30.02311893660071</v>
+        <v>53.44550833019914</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0.9126724363057656</v>
+        <v>0.7529275894504066</v>
       </c>
       <c r="K12" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M12" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>-0.7280362272499774</v>
+        <v>1.056222429240911</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>6835</v>
+        <v>6708</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>圓裕</t>
+          <t>天擎</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>716.9568916986983</v>
+        <v>884.5559222994942</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>32</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,16 +1135,16 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>61.22944841977671</v>
+        <v>79.44363605627419</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>15.22412841430277</v>
+        <v>20.36940608717189</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>2.77292033102005</v>
+        <v>2.555592229949426</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L13" s="2" t="n">
         <v>0</v>
@@ -1153,31 +1153,31 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>0.1103149757219049</v>
+        <v>2.927787203801312</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, foreign_buy_3d, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>6715</v>
+        <v>6743</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>嘉基</t>
+          <t>安普新</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>716.076581322978</v>
+        <v>863.9503329154978</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>480.5</v>
+        <v>35.6</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1188,13 +1188,13 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>65.66997362416829</v>
+        <v>88.02911171666669</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>24.48015816419888</v>
+        <v>33.62905808868051</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>1.311343486090299</v>
+        <v>1.995033291549784</v>
       </c>
       <c r="K14" s="2" t="n">
         <v>0</v>
@@ -1206,31 +1206,31 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>7.595844019537175</v>
+        <v>0.6138116182526991</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>6525</v>
+        <v>6788</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>捷敏-KY</t>
+          <t>華景電</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>713.1601895520506</v>
+        <v>863.6666390563694</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>140</v>
+        <v>376.5</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1241,16 +1241,16 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>57.24072546953302</v>
+        <v>65.4897792181921</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>13.17901674066669</v>
+        <v>15.69109678509287</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>2.827913531966264</v>
+        <v>3.27644233089846</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L15" s="2" t="n">
         <v>0</v>
@@ -1259,31 +1259,31 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>1.471029358399821</v>
+        <v>4.658548555751873</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, breakout_volume_confirm, mfi_strong</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>6668</v>
+        <v>6640</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>中揚光</t>
+          <t>均華</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>711.6997970301549</v>
+        <v>863.5031017758334</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>48.25</v>
+        <v>1165</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,16 +1294,16 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>63.65545917814354</v>
+        <v>56.64606416528541</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>46.98756651982485</v>
+        <v>20.22714139886987</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>1.583172095615539</v>
+        <v>0.9503101775833396</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16" s="2" t="n">
         <v>0</v>
@@ -1312,31 +1312,31 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>-0.030397807168871</v>
+        <v>-2.604722865565156</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>6742</v>
+        <v>6805</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>澤米</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>710.5323674271469</v>
+        <v>858.6314336585361</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>60.2</v>
+        <v>2450</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,16 +1347,16 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>74.01853827923951</v>
+        <v>59.23059786727048</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>49.06471080645658</v>
+        <v>35.10981643991597</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>2.153236742714691</v>
+        <v>1.742217057679818</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L17" s="2" t="n">
         <v>0</v>
@@ -1365,31 +1365,31 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>0.9330729051840794</v>
+        <v>-8.594831505177183</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>6491</v>
+        <v>6532</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>晶碩</t>
+          <t>瑞耘</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>706.9742059257893</v>
+        <v>835.2433821739991</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>403</v>
+        <v>112</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1400,13 +1400,13 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>54.88601865762492</v>
+        <v>63.14265157163306</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>31.03164876356369</v>
+        <v>45.63003998280781</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>1.951560298710488</v>
+        <v>1.451286790385561</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>0</v>
@@ -1418,31 +1418,31 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>1.021037906264315</v>
+        <v>1.74535992987291</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>6690</v>
+        <v>6715</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>安碁資訊</t>
+          <t>嘉基</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>696.4910229163221</v>
+        <v>826.076581322978</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>177</v>
+        <v>480.5</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,49 +1453,49 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>55.38133768262722</v>
+        <v>65.66997362530688</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>34.34169596762383</v>
+        <v>24.48015818092082</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>0.5138893827397127</v>
+        <v>1.311343486090299</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M19" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>-0.5558035363214398</v>
+        <v>7.595844019870984</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>6788</v>
+        <v>6834</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>華景電</t>
+          <t>天二科技</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>693.6666390563691</v>
+        <v>823.2532437362908</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>376.5</v>
+        <v>125.5</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,16 +1506,16 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>65.48977923196198</v>
+        <v>64.56409701004588</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>15.69109669509834</v>
+        <v>38.04771684724379</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>3.27644233089846</v>
+        <v>1.51665719257069</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L20" s="2" t="n">
         <v>0</v>
@@ -1524,31 +1524,31 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>4.658548554194036</v>
+        <v>2.032747504334465</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>6834</v>
+        <v>6488</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>天二科技</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>683.2532437362908</v>
+        <v>819.826876732334</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>125.5</v>
+        <v>1180</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,49 +1559,49 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>64.56409701167844</v>
+        <v>69.75730876396372</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>38.04771691523985</v>
+        <v>17.78037895454254</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>1.51665719257069</v>
+        <v>1.565360299462272</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M21" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>2.032747504312233</v>
+        <v>30.15606303260411</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, invest_trust_buy_2d, bb_squeeze_breakout, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>6642</v>
+        <v>6789</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>富致</t>
+          <t>采鈺</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>679.2650976638191</v>
+        <v>796.2571509717191</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>82.09999999999999</v>
+        <v>488</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,49 +1612,49 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>57.26497201123627</v>
+        <v>59.68050706297107</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>22.1051761519803</v>
+        <v>17.01564875276071</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>1.027234042553191</v>
+        <v>0.9886649041937836</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L22" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M22" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>0.6546635148552594</v>
+        <v>4.108698191861322</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>6743</v>
+        <v>6642</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>安普新</t>
+          <t>富致</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>663.9503329154978</v>
+        <v>794.2650976638191</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>35.6</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,13 +1665,13 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>88.02911185334081</v>
+        <v>57.26497198162031</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>33.62905796363939</v>
+        <v>22.10517611092567</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>1.995033291549784</v>
+        <v>1.027234042553191</v>
       </c>
       <c r="K23" s="2" t="n">
         <v>0</v>
@@ -1683,31 +1683,31 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>0.6138116181191764</v>
+        <v>0.6546635150555412</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>6640</v>
+        <v>6485</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>均華</t>
+          <t>點序</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>663.5031017758334</v>
+        <v>774.1423012451198</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>1165</v>
+        <v>79</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,16 +1718,16 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>56.64606417307557</v>
+        <v>65.35183511105869</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>20.22714133780156</v>
+        <v>34.26278886341307</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.9503101775833396</v>
+        <v>1.795041528588462</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L24" s="2" t="n">
         <v>0</v>
@@ -1736,31 +1736,31 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>-2.604722865787837</v>
+        <v>2.131629172921472</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>6693</v>
+        <v>6719</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>廣閎科</t>
+          <t>力智</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>651.319815731197</v>
+        <v>771.0178700619214</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>215.5</v>
+        <v>191.5</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,16 +1771,16 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>63.64646784296225</v>
+        <v>53.04849483672293</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>25.72914488421985</v>
+        <v>17.98050688786709</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>1.100543443328191</v>
+        <v>1.698568414992002</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L25" s="2" t="n">
         <v>0</v>
@@ -1789,31 +1789,31 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>3.255196184166107</v>
+        <v>2.013994472913895</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, dealer_buy_3d, breakout_volume_confirm, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>6532</v>
+        <v>6770</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>瑞耘</t>
+          <t>力積電</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>635.2433821739991</v>
+        <v>764.7430043130317</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>112</v>
+        <v>75.8</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,29 +1824,29 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>63.14265160362785</v>
+        <v>58.48494469931325</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>45.6300399709163</v>
+        <v>12.62086351908755</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>1.451286790385561</v>
+        <v>0.9950024036977724</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L26" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M26" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>1.745359929761646</v>
+        <v>0.3705723280059185</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -1863,7 +1863,7 @@
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>622.7466424366042</v>
+        <v>762.7466424366048</v>
       </c>
       <c r="E27" s="2" t="n">
         <v>151.5</v>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>58.79405976131271</v>
+        <v>58.79405975361428</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>50.65870267938124</v>
+        <v>50.65870270501311</v>
       </c>
       <c r="J27" s="2" t="n">
         <v>0.3223899158156122</v>
@@ -1895,31 +1895,31 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>0.1998630180124001</v>
+        <v>0.1998630181236818</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>6488</v>
+        <v>6811</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>宏碁資訊</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>619.8268767323336</v>
+        <v>739.9866181586093</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>1180</v>
+        <v>246.5</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,49 +1930,49 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>69.75730875734737</v>
+        <v>55.75132728665289</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>17.78037895454254</v>
+        <v>30.02311893660071</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>1.565360299462272</v>
+        <v>0.9126724363057656</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L28" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M28" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>30.15606303360567</v>
+        <v>-0.728036227027431</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, invest_trust_buy_2d, bb_squeeze_breakout, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>6530</v>
+        <v>6799</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>創威</t>
+          <t>來頡</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>618.0843677296475</v>
+        <v>736.2625018978576</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>98.5</v>
+        <v>91.8</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,16 +1983,16 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>54.24572212114877</v>
+        <v>68.55854647807146</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>33.99962254596618</v>
+        <v>30.60250715011059</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.4864243389827517</v>
+        <v>1.127674927480242</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L29" s="2" t="n">
         <v>0</v>
@@ -2001,31 +2001,31 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>-0.326333741099059</v>
+        <v>1.255645812045626</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>6643</v>
+        <v>6654</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>M31</t>
+          <t>天正國際</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>608.5697245010223</v>
+        <v>720.6926023924007</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>508</v>
+        <v>219</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,16 +2036,16 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>59.55328674705712</v>
+        <v>61.23565635525432</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>33.37411051127713</v>
+        <v>25.57437086717769</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.7028728202204531</v>
+        <v>0.5139455316557392</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L30" s="2" t="n">
         <v>0</v>
@@ -2054,31 +2054,31 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>7.131108835684216</v>
+        <v>0.7946637882176057</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>6667</v>
+        <v>6835</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>信紘科</t>
+          <t>圓裕</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>607.412315347383</v>
+        <v>716.9568916986882</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>264.5</v>
+        <v>32</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,16 +2089,16 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>65.19740489377921</v>
+        <v>61.22944919772941</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>40.9079571171212</v>
+        <v>15.22412835397147</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.8528507706283147</v>
+        <v>2.77292033102005</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L31" s="2" t="n">
         <v>0</v>
@@ -2107,31 +2107,31 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>0.8106649033798323</v>
+        <v>0.1103149750208934</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>6485</v>
+        <v>6533</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>點序</t>
+          <t>晶心科</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>604.1423012451201</v>
+        <v>715.1314317110165</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>79</v>
+        <v>336</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,13 +2142,13 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>65.35183512553311</v>
+        <v>67.09561850600562</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>34.26278887806853</v>
+        <v>33.86548902111736</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>1.795041528588462</v>
+        <v>1.482111919048665</v>
       </c>
       <c r="K32" s="2" t="n">
         <v>0</v>
@@ -2160,31 +2160,31 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>2.131629172832469</v>
+        <v>10.5284981420132</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>6505</v>
+        <v>6668</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>台塑化</t>
+          <t>中揚光</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>599.9014034948467</v>
+        <v>711.6997970301549</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>98.59999999999999</v>
+        <v>48.25</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,13 +2195,13 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>69.6468278642227</v>
+        <v>63.65545916487356</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>53.44550827650467</v>
+        <v>46.98756653906187</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.7529275894504066</v>
+        <v>1.583172095615539</v>
       </c>
       <c r="K33" s="2" t="n">
         <v>0</v>
@@ -2213,31 +2213,31 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>1.056222428873727</v>
+        <v>-0.0303978073023989</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>6719</v>
+        <v>6491</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>力智</t>
+          <t>晶碩</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>581.0178700619214</v>
+        <v>706.9742059257893</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>191.5</v>
+        <v>403</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,16 +2248,16 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>53.04849487560281</v>
+        <v>54.88601862840656</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>17.98050682793015</v>
+        <v>31.03164876294269</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>1.698568414992002</v>
+        <v>1.951560298710488</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L34" s="2" t="n">
         <v>0</v>
@@ -2266,31 +2266,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>2.0139944724688</v>
+        <v>1.02103790726572</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>volume_break, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>6588</v>
+        <v>6558</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>東典光電</t>
+          <t>興能高</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>566.2586094987266</v>
+        <v>699.9412179129471</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>111.5</v>
+        <v>25.4</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,16 +2301,16 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>53.03027416641896</v>
+        <v>56.39949778144334</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>22.47024807193621</v>
+        <v>26.92633218207163</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.3892830505003652</v>
+        <v>0.9317162658921072</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L35" s="2" t="n">
         <v>0</v>
@@ -2319,31 +2319,31 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>-0.663782370677831</v>
+        <v>0.2533548421342896</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>6789</v>
+        <v>6573</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>采鈺</t>
+          <t>虹揚-KY</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>566.25715097172</v>
+        <v>697.2675512143543</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>488</v>
+        <v>16.55</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,16 +2354,16 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>59.68050716098864</v>
+        <v>49.86790911909903</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>17.01564879742784</v>
+        <v>18.02671924523381</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.9886649041937836</v>
+        <v>2.816883270701731</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L36" s="2" t="n">
         <v>0</v>
@@ -2372,31 +2372,31 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>4.108698188968273</v>
+        <v>0.0964082335001248</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>6722</v>
+        <v>6690</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>輝創</t>
+          <t>安碁資訊</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>538.295438937113</v>
+        <v>696.4910229163221</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>33.05</v>
+        <v>177</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,13 +2407,13 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>55.33340842532868</v>
+        <v>55.38133752737357</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>19.06073622001061</v>
+        <v>34.34169587489404</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>3.324357290923755</v>
+        <v>0.5138893827397127</v>
       </c>
       <c r="K37" s="2" t="n">
         <v>0</v>
@@ -2425,31 +2425,31 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>0.0558963703346645</v>
+        <v>-0.5558035354312767</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>6770</v>
+        <v>6695</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>力積電</t>
+          <t>芯鼎</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>534.7430043130317</v>
+        <v>671.3988579668778</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>75.8</v>
+        <v>52.7</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,16 +2460,16 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>58.4849447076254</v>
+        <v>57.18917043365243</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>12.62086351838141</v>
+        <v>24.47316291988021</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.9950024036977724</v>
+        <v>1.179583550895674</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L38" s="2" t="n">
         <v>0</v>
@@ -2478,51 +2478,51 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>0.3705723279391575</v>
+        <v>0.6450950403978952</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>6806</v>
+        <v>6693</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>森崴能源</t>
+          <t>廣閎科</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>528.7768356926886</v>
+        <v>651.319815731197</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>3.51</v>
+        <v>215.5</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G39" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>31.69502174203133</v>
+        <v>63.64646784826728</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>32.59322192025892</v>
+        <v>25.72914498541272</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>2.013053626871306</v>
+        <v>1.100543443328191</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>0.4112819962396501</v>
+        <v>3.255196183876813</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>6680</v>
+        <v>6530</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>鑫創電子</t>
+          <t>創威</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>525.8661172432666</v>
+        <v>618.0843677296475</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>51.5</v>
+        <v>98.5</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,13 +2566,13 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>52.03112899850045</v>
+        <v>54.2457220924823</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>7.281108676292325</v>
+        <v>33.99962256825849</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>2.56041356775342</v>
+        <v>0.4864243389827517</v>
       </c>
       <c r="K40" s="2" t="n">
         <v>0</v>
@@ -2584,31 +2584,31 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>0.2886595568167988</v>
+        <v>-0.3263337406539675</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, volume_break, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, williams_r_recovery, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>6771</v>
+        <v>6643</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>平和環保-創</t>
+          <t>M31</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>521.9040564576216</v>
+        <v>608.5697245010223</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>42.5</v>
+        <v>508</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,16 +2619,16 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>57.86119851092397</v>
+        <v>59.55328674979972</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>21.2830350602602</v>
+        <v>33.37411052579854</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.5261649143248167</v>
+        <v>0.7028728202204531</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L41" s="2" t="n">
         <v>0</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>-0.0041539974366965</v>
+        <v>7.131108837019458</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>6654</v>
+        <v>6667</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>天正國際</t>
+          <t>信紘科</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>520.6926023924007</v>
+        <v>607.412315347383</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>219</v>
+        <v>264.5</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,16 +2672,16 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>61.23565634770298</v>
+        <v>65.19740479970073</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>25.57437070795661</v>
+        <v>40.90795721125316</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.5139455316557392</v>
+        <v>0.8528507706283147</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L42" s="2" t="n">
         <v>0</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>0.7946637883288776</v>
+        <v>0.8106649031572921</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>6533</v>
+        <v>6821</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>晶心科</t>
+          <t>聯寶</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>515.1314317110164</v>
+        <v>578.2403179434424</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>336</v>
+        <v>45.5</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,13 +2725,13 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>67.0956185175425</v>
+        <v>63.15513290458606</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>33.86548901313939</v>
+        <v>21.39842324714256</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>1.482111919048665</v>
+        <v>5.40437947395736</v>
       </c>
       <c r="K43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>10.52849814156813</v>
+        <v>0.6869675379566268</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, bb_squeeze_breakout, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>6830</v>
+        <v>6588</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>汎銓</t>
+          <t>東典光電</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>507.3084827018595</v>
+        <v>566.2586094987266</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>550</v>
+        <v>111.5</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,13 +2778,13 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>55.61642318281841</v>
+        <v>53.03027417264336</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>25.47696543663492</v>
+        <v>22.47024812468172</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>1.116719430469057</v>
+        <v>0.3892830505003652</v>
       </c>
       <c r="K44" s="2" t="n">
         <v>0</v>
@@ -2796,31 +2796,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>-5.051238173573648</v>
+        <v>-0.6637823707890935</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>6534</v>
+        <v>6655</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>正瀚-創</t>
+          <t>科定</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>504.9473836258911</v>
+        <v>563.1365532639991</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>93</v>
+        <v>125.5</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,16 +2831,16 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>61.04615279304198</v>
+        <v>52.19147676141133</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>14.05415355147446</v>
+        <v>12.32517463444113</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>2.915433156010269</v>
+        <v>0.413655326399906</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L45" s="2" t="n">
         <v>0</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>0.3439178054497788</v>
+        <v>-0.5784837379660228</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, breakout_volume_confirm, mfi_strong</t>
+          <t>breakout_20d, market_above_ma60, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>6782</v>
+        <v>6725</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>視陽</t>
+          <t>矽科宏晟</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>503.9912299367719</v>
+        <v>549.8634824053941</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,16 +2884,16 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>48.04221617838616</v>
+        <v>49.22836096157073</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>19.85272752991212</v>
+        <v>18.23302382737506</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.7850900229501893</v>
+        <v>1.301908640500677</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>-1.705453657459773</v>
+        <v>2.256141999085621</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>6674</v>
+        <v>6771</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>鋐寶科技</t>
+          <t>平和環保-創</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>502.3113521194628</v>
+        <v>541.9040564576219</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>18.3</v>
+        <v>42.5</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,16 +2937,16 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>70.15605311070487</v>
+        <v>57.86119844361212</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>36.93872886837656</v>
+        <v>21.28303501109118</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.3297012846418027</v>
+        <v>0.5261649143248167</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L47" s="2" t="n">
         <v>0</v>
@@ -2955,7 +2955,7 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>0.1685735650543571</v>
+        <v>-0.0041539974144385</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
@@ -2965,21 +2965,21 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>6510</v>
+        <v>6722</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>精測</t>
+          <t>輝創</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>495.8852349347927</v>
+        <v>538.2954389371106</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>3105</v>
+        <v>33.05</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,16 +2990,16 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>46.79290530297407</v>
+        <v>55.33340851045777</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>23.97496594327822</v>
+        <v>19.06073626538707</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.89309124799904</v>
+        <v>3.324357290923755</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L48" s="2" t="n">
         <v>0</v>
@@ -3008,48 +3008,48 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>-65.55764442297132</v>
+        <v>0.0558963703346645</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, dealer_buy_3d, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>6671</v>
+        <v>6806</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>三能-KY</t>
+          <t>森崴能源</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>495.2168598716692</v>
+        <v>528.7768356926886</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>23.3</v>
+        <v>3.51</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G49" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>57.79635361382972</v>
+        <v>31.69441612163047</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>18.19393174360885</v>
+        <v>32.59322162613325</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.6833001444691734</v>
+        <v>2.013053626871306</v>
       </c>
       <c r="K49" s="2" t="n">
         <v>0</v>
@@ -3061,31 +3061,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>0.0386407264207591</v>
+        <v>0.4112819621929588</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, bb_squeeze_breakout, cci_momentum, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>6799</v>
+        <v>6781</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>來頡</t>
+          <t>AES-KY</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>486.2625018978577</v>
+        <v>527.6871349685036</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>91.8</v>
+        <v>1050</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,16 +3096,16 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>68.55854647548739</v>
+        <v>53.11026518383969</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>30.6025070795998</v>
+        <v>11.74690356845408</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>1.127674927480242</v>
+        <v>1.615290928770729</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>1.255645811845329</v>
+        <v>4.487252190782037</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>6589</v>
+        <v>6680</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>台康生技</t>
+          <t>鑫創電子</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>477.1660404641492</v>
+        <v>525.8661172432666</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>50.7</v>
+        <v>51.5</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,13 +3149,13 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>51.21561145070602</v>
+        <v>52.03112884819053</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>20.69896375278613</v>
+        <v>7.28110816581701</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.6778841817662256</v>
+        <v>2.56041356775342</v>
       </c>
       <c r="K51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>0.0350652287500168</v>
+        <v>0.2886595721054834</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, volume_break, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, williams_r_recovery, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>6558</v>
+        <v>6517</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>興能高</t>
+          <t>保勝光學</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>474.9412179129412</v>
+        <v>520.6787817830624</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>25.4</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,16 +3202,16 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>56.39949748540111</v>
+        <v>53.8727999942276</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>26.92633219051623</v>
+        <v>10.926507241749</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.9317162658921072</v>
+        <v>1.401285759296467</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L52" s="2" t="n">
         <v>0</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>0.2533548423012011</v>
+        <v>0.2592034183254217</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, foreign_buy_3d, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>6486</v>
+        <v>6735</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>互動</t>
+          <t>美達科技</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>474.4598739893951</v>
+        <v>514.6899761179325</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>78</v>
+        <v>66.3</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,16 +3255,16 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>40.69702039252999</v>
+        <v>56.53116281049422</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>44.78119452533534</v>
+        <v>23.05624980881336</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>3.850240940903497</v>
+        <v>1.037480842384612</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>-0.3675988572774635</v>
+        <v>0.7740595907627774</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>6538</v>
+        <v>6534</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>倉和</t>
+          <t>正瀚-創</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>474.0521741325892</v>
+        <v>504.9473836258915</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>335.5</v>
+        <v>93</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,13 +3308,13 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>51.15248623168655</v>
+        <v>61.04615249218641</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>52.25858250340435</v>
+        <v>14.05415346275153</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.9684548106318546</v>
+        <v>2.915433156010269</v>
       </c>
       <c r="K54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>-11.25823787322892</v>
+        <v>0.3439178060729009</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>6573</v>
+        <v>6782</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>虹揚-KY</t>
+          <t>視陽</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>472.2675512143544</v>
+        <v>503.991229936772</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>16.55</v>
+        <v>229</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,13 +3361,13 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>49.86790914142102</v>
+        <v>48.04221617311895</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>18.0267191610604</v>
+        <v>19.85272747666083</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>2.816883270701731</v>
+        <v>0.7850900229501893</v>
       </c>
       <c r="K55" s="2" t="n">
         <v>0</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>0.0964082335023511</v>
+        <v>-1.705453656903387</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>6756</v>
+        <v>6674</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>威鋒電子</t>
+          <t>鋐寶科技</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>453.5276484090608</v>
+        <v>502.3113521194628</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>98.2</v>
+        <v>18.3</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,13 +3414,13 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>50.85030760706541</v>
+        <v>70.15605326181553</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>12.27676614204378</v>
+        <v>36.93872909431006</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>1.055136416430684</v>
+        <v>0.3297012846418027</v>
       </c>
       <c r="K56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>0.0984588475315876</v>
+        <v>0.1685735650766087</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>6725</v>
+        <v>6830</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>矽科宏晟</t>
+          <t>汎銓</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>434.8634824053942</v>
+        <v>497.3084827018595</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>223</v>
+        <v>550</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,16 +3467,16 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>49.22836146757154</v>
+        <v>55.61642316605774</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>18.23302357392042</v>
+        <v>25.47696547872355</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>1.301908640500677</v>
+        <v>1.116719430469057</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>2.256141992631909</v>
+        <v>-5.051238173462384</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>6689</v>
+        <v>6794</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>伊雲谷</t>
+          <t>向榮生技-創</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>433.9977234816719</v>
+        <v>496.915747074198</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>63.1</v>
+        <v>76</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,13 +3520,13 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>47.31394664199864</v>
+        <v>52.57398296721567</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>24.49691332639695</v>
+        <v>17.70976355232252</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.285829590901388</v>
+        <v>2.769299665441102</v>
       </c>
       <c r="K58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>-0.26529281017746</v>
+        <v>0.1249136722982695</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>6591</v>
+        <v>6552</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>動力-KY</t>
+          <t>易華電</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>428.6844166967923</v>
+        <v>496.5772933272684</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>42.9</v>
+        <v>24.95</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,16 +3573,16 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>46.94483668739026</v>
+        <v>55.60884400721659</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>28.69393745091457</v>
+        <v>18.20353108049943</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>1.024913190930764</v>
+        <v>1.306960390655568</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>0.029239426570789</v>
+        <v>0.1643837138425284</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>6695</v>
+        <v>6510</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>芯鼎</t>
+          <t>精測</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>421.3988579668775</v>
+        <v>495.8852349347926</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>52.7</v>
+        <v>3105</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,13 +3626,13 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>57.18917051892748</v>
+        <v>46.79290530451259</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>24.47316291396454</v>
+        <v>23.97496598490936</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>1.179583550895674</v>
+        <v>0.89309124799904</v>
       </c>
       <c r="K60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>0.6450950403645084</v>
+        <v>-65.55764442319389</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, dealer_buy_3d, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>6679</v>
+        <v>6671</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>鈺太</t>
+          <t>三能-KY</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>420.2567947242639</v>
+        <v>495.2168598716692</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>206.5</v>
+        <v>23.3</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,13 +3679,13 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>53.66213562242623</v>
+        <v>57.79638107902672</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>14.28184535829684</v>
+        <v>18.19392949829114</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.718375314844098</v>
+        <v>0.6833001444691734</v>
       </c>
       <c r="K61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>1.707453220551259</v>
+        <v>0.0386407177972304</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, bb_squeeze_breakout, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>6684</v>
+        <v>6541</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>安格</t>
+          <t>泰福-KY</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>417.6890213293837</v>
+        <v>492.4925569730354</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>49.05</v>
+        <v>31.45</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,16 +3732,16 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>54.305191776321</v>
+        <v>46.57004800647444</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>27.10649612086668</v>
+        <v>20.23535425133006</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.7959862063544726</v>
+        <v>1.767297603431134</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>0.3049874450944649</v>
+        <v>0.2057168783767169</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>6683</v>
+        <v>6589</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>雍智科技</t>
+          <t>台康生技</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>417.3903325318682</v>
+        <v>477.1660404641492</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>1440</v>
+        <v>50.7</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,16 +3785,16 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>49.39363644949023</v>
+        <v>51.21561146591186</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>19.10966421013356</v>
+        <v>20.69896372815181</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.8788111699241419</v>
+        <v>0.6778841817662256</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>-13.08786414491439</v>
+        <v>0.0350652288612878</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>6579</v>
+        <v>6486</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>研揚</t>
+          <t>互動</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>414.9169397071389</v>
+        <v>474.4598739893951</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>158</v>
+        <v>78</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,16 +3838,16 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>57.65563554871524</v>
+        <v>40.69702036863322</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>15.58613311760201</v>
+        <v>44.78119456006631</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.94869092368205</v>
+        <v>3.850240940903497</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>1.255544666979391</v>
+        <v>-0.3675988573664788</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>6781</v>
+        <v>6538</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>AES-KY</t>
+          <t>倉和</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>412.6871349685036</v>
+        <v>474.0521741325892</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>1050</v>
+        <v>335.5</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,13 +3891,13 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>53.11026505647533</v>
+        <v>51.15248623078622</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>11.7469035042107</v>
+        <v>52.25858251614418</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>1.615290928770729</v>
+        <v>0.9684548106318546</v>
       </c>
       <c r="K65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>4.487252207472824</v>
+        <v>-11.25823787313989</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>6821</v>
+        <v>6550</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>聯寶</t>
+          <t>北極星藥業-KY</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>408.2403179434444</v>
+        <v>466.6895621757138</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>45.5</v>
+        <v>16.2</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,16 +3944,16 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>63.15513290244132</v>
+        <v>70.22089226025183</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>21.39842322827338</v>
+        <v>29.93085865718579</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>5.40437947395736</v>
+        <v>0.6848968793338485</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>0.6869675378453668</v>
+        <v>0.7973789064971902</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, adx_trending, bb_squeeze_breakout, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, adx_trending, stronger_than_market, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>6517</v>
+        <v>6796</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>保勝光學</t>
+          <t>晉弘</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>405.6787817830624</v>
+        <v>458.1727519046976</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>66.40000000000001</v>
+        <v>57</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,16 +3997,16 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>53.87280000791058</v>
+        <v>57.45254142058555</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>10.92650721200025</v>
+        <v>23.56677665868211</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>1.401285759296467</v>
+        <v>0.9723730460623458</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>0.2592034183476704</v>
+        <v>0.8003713584881009</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, foreign_buy_3d, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, adx_trending, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>6735</v>
+        <v>6756</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>美達科技</t>
+          <t>威鋒電子</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>399.6899761179322</v>
+        <v>453.5276484090608</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>66.3</v>
+        <v>98.2</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,16 +4050,16 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>56.53116281268768</v>
+        <v>50.85030763918633</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>23.05624980682654</v>
+        <v>12.27676616213147</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>1.037480842384612</v>
+        <v>1.055136416430684</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>0.7740595907516515</v>
+        <v>0.09845884762060519</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>6732</v>
+        <v>6689</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>昇佳電子</t>
+          <t>伊雲谷</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>388.5667121449221</v>
+        <v>433.9977234816719</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>153.5</v>
+        <v>63.1</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,13 +4103,13 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>55.51630833064764</v>
+        <v>47.31394648997229</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>16.89520052348433</v>
+        <v>24.49691334630669</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>1.738987276586245</v>
+        <v>0.285829590901388</v>
       </c>
       <c r="K69" s="2" t="n">
         <v>0</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>1.187313055334465</v>
+        <v>-0.2652928098881508</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>6552</v>
+        <v>6591</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>易華電</t>
+          <t>動力-KY</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>386.5772933272683</v>
+        <v>428.6844166968081</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>24.95</v>
+        <v>42.9</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,16 +4156,16 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>55.60884404218662</v>
+        <v>46.94483693057797</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>18.2035310448812</v>
+        <v>28.69393747461609</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>1.306960390655568</v>
+        <v>1.024913190930764</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>0.1643837138536569</v>
+        <v>0.0292394266375502</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>6669</v>
+        <v>6679</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>鈺太</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>386.3503249024299</v>
+        <v>420.2567947242638</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>2150</v>
+        <v>206.5</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,13 +4209,13 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>28.01675529806421</v>
+        <v>53.66213563357309</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>46.70744565011376</v>
+        <v>14.28184538959275</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.7984083467166709</v>
+        <v>0.718375314844098</v>
       </c>
       <c r="K71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>114.4589135343702</v>
+        <v>1.707453220439977</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>6641</v>
+        <v>6684</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>基士德-KY</t>
+          <t>安格</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>383.7916452238846</v>
+        <v>417.6890213293833</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>17.05</v>
+        <v>49.05</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,16 +4262,16 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>51.31057595627778</v>
+        <v>54.305191776321</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>8.291026558423823</v>
+        <v>27.10649612346995</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>1.711684742978638</v>
+        <v>0.7959862063544726</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>0.2056587850381813</v>
+        <v>0.3049874452947554</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>6794</v>
+        <v>6683</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>向榮生技-創</t>
+          <t>雍智科技</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>381.9157470741979</v>
+        <v>417.3903325318682</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>76</v>
+        <v>1440</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,13 +4315,13 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>52.57398296721567</v>
+        <v>49.39363646050628</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>17.70976350869994</v>
+        <v>19.10966426457201</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>2.769299665441102</v>
+        <v>0.8788111699241419</v>
       </c>
       <c r="K73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>0.1249136720312225</v>
+        <v>-13.08786414624953</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>6768</v>
+        <v>6579</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>志強-KY</t>
+          <t>研揚</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>378.3978338793268</v>
+        <v>414.9169397071389</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>63.1</v>
+        <v>158</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,16 +4368,16 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>45.36734930428355</v>
+        <v>57.65563565296024</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>20.06207729221012</v>
+        <v>15.58613319350443</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.7431009599823311</v>
+        <v>0.94869092368205</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L74" s="2" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>0.3145185696070867</v>
+        <v>1.255544666534283</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>6541</v>
+        <v>6669</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>泰福-KY</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>377.4925569730354</v>
+        <v>406.3503249024299</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>31.45</v>
+        <v>2150</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,16 +4421,16 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>46.57004808727874</v>
+        <v>28.0167553089976</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>20.23535423376368</v>
+        <v>46.70744568913916</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>1.767297603431134</v>
+        <v>0.7984083467166709</v>
       </c>
       <c r="K75" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>0.2057168781541707</v>
+        <v>114.4589135555119</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>6512</v>
+        <v>6732</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>啟發電</t>
+          <t>昇佳電子</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>374.1942726883955</v>
+        <v>388.5667121449221</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>20.2</v>
+        <v>153.5</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,13 +4474,13 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>52.07154397761146</v>
+        <v>55.51630838160587</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>7.39126167948767</v>
+        <v>16.89520052348433</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.5173606535775465</v>
+        <v>1.738987276586245</v>
       </c>
       <c r="K76" s="2" t="n">
         <v>0</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>0.1762138018212741</v>
+        <v>1.187313055779542</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>6655</v>
+        <v>6641</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>科定</t>
+          <t>基士德-KY</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>363.1365532639991</v>
+        <v>383.7916452238846</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>125.5</v>
+        <v>17.05</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,16 +4527,16 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>52.19147676052717</v>
+        <v>51.31057596450598</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>12.3251748958321</v>
+        <v>8.291026657931868</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.413655326399906</v>
+        <v>1.711684742978638</v>
       </c>
       <c r="K77" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L77" s="2" t="n">
         <v>0</v>
@@ -4545,31 +4545,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>-0.5784837378547447</v>
+        <v>0.2056587849936714</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>breakout_20d, market_above_ma60, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>6666</v>
+        <v>6768</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>羅麗芬-KY</t>
+          <t>志強-KY</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>361.7815705863865</v>
+        <v>378.3978338793269</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>45.35</v>
+        <v>63.1</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,13 +4580,13 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>57.01717967381371</v>
+        <v>45.36734974688013</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>10.1523795717307</v>
+        <v>20.06207720239097</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>1.32543436214995</v>
+        <v>0.7431009599823311</v>
       </c>
       <c r="K78" s="2" t="n">
         <v>0</v>
@@ -4598,31 +4598,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>0.0521961531148122</v>
+        <v>0.3145185688281842</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>6577</v>
+        <v>6512</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>勁豐</t>
+          <t>啟發電</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>360.7194218710737</v>
+        <v>374.1942726883955</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>80.5</v>
+        <v>20.2</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,13 +4633,13 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>54.18568646855796</v>
+        <v>52.07154398024571</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>13.18006610676445</v>
+        <v>7.39126172101791</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.2937461064580882</v>
+        <v>0.5173606535775465</v>
       </c>
       <c r="K79" s="2" t="n">
         <v>0</v>
@@ -4651,31 +4651,31 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>0.183851410671447</v>
+        <v>0.1762138018546548</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>6561</v>
+        <v>6592</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>是方</t>
+          <t>和潤企業</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>355.230554104457</v>
+        <v>372.5862496449501</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>314</v>
+        <v>55.4</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,13 +4686,13 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>47.59860537241671</v>
+        <v>18.51340881521088</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>21.81289759190213</v>
+        <v>31.66488743098945</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.8380825966049564</v>
+        <v>2.582062336255115</v>
       </c>
       <c r="K80" s="2" t="n">
         <v>0</v>
@@ -4704,31 +4704,31 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>0.2840438419732547</v>
+        <v>-0.3236201060489647</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>6692</v>
+        <v>6666</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>進能服</t>
+          <t>羅麗芬-KY</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>354.9383130083756</v>
+        <v>361.7815705863865</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>23.25</v>
+        <v>45.35</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,13 +4739,13 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>51.17604395224743</v>
+        <v>57.01717975613706</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>7.867925110264339</v>
+        <v>10.15237957210605</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.2045659111365682</v>
+        <v>1.32543436214995</v>
       </c>
       <c r="K81" s="2" t="n">
         <v>0</v>
@@ -4757,31 +4757,31 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>0.2330593277457888</v>
+        <v>0.0521961530591743</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>6831</v>
+        <v>6577</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>邁科</t>
+          <t>勁豐</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>352.0133377482795</v>
+        <v>360.7194218710737</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>489</v>
+        <v>80.5</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,13 +4792,13 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>37.42959413111147</v>
+        <v>54.18568641506442</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>24.29979647613385</v>
+        <v>13.18006610676444</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.9115539804097812</v>
+        <v>0.2937461064580882</v>
       </c>
       <c r="K82" s="2" t="n">
         <v>0</v>
@@ -4810,31 +4810,31 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>-1.685258920263774</v>
+        <v>0.183851410671447</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>6739</v>
+        <v>6561</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>竹陞科技</t>
+          <t>是方</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>345.4304601184473</v>
+        <v>355.230554104457</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>1125</v>
+        <v>314</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,13 +4845,13 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>51.19071602100838</v>
+        <v>47.59860568041951</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>10.22666940471107</v>
+        <v>21.81289754254664</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.8291873520155691</v>
+        <v>0.8380825966049564</v>
       </c>
       <c r="K83" s="2" t="n">
         <v>0</v>
@@ -4863,31 +4863,31 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>-1.021137659621026</v>
+        <v>0.2840438405267509</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>6645</v>
+        <v>6692</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>金萬林-創</t>
+          <t>進能服</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>343.4170303028184</v>
+        <v>354.9383130083754</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>12.75</v>
+        <v>23.25</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,13 +4898,13 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>50.81070734870302</v>
+        <v>51.17604395837433</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>26.41300075487823</v>
+        <v>7.867925113823182</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0.651438836790813</v>
+        <v>0.2045659111365682</v>
       </c>
       <c r="K84" s="2" t="n">
         <v>0</v>
@@ -4916,31 +4916,31 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>0.0605320738889344</v>
+        <v>0.2330593276456459</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>6584</v>
+        <v>6831</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>南俊國際</t>
+          <t>邁科</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>341.4199016504267</v>
+        <v>352.0133377482797</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>541</v>
+        <v>489</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,13 +4951,13 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>43.44683477015019</v>
+        <v>37.42959412818328</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>19.01305257127052</v>
+        <v>24.29979642237436</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>2.247591968666175</v>
+        <v>0.9115539804097812</v>
       </c>
       <c r="K85" s="2" t="n">
         <v>0</v>
@@ -4969,31 +4969,31 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>-2.791248251975359</v>
+        <v>-1.685258920486351</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>6494</v>
+        <v>6739</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>九齊</t>
+          <t>竹陞科技</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>338.9419479872615</v>
+        <v>345.4304601184477</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>52.9</v>
+        <v>1125</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,13 +5004,13 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>53.21813011542149</v>
+        <v>51.1907159850556</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>10.82376525061812</v>
+        <v>10.2266693867081</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>0.8848343262874399</v>
+        <v>0.8291873520155691</v>
       </c>
       <c r="K86" s="2" t="n">
         <v>0</v>
@@ -5022,31 +5022,31 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>0.3402770854095485</v>
+        <v>-1.021137657506957</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>6741</v>
+        <v>6645</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>91APP*-KY</t>
+          <t>金萬林-創</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>336.5454925231704</v>
+        <v>343.4170303028184</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>54.9</v>
+        <v>12.75</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,13 +5057,13 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>34.98015768420832</v>
+        <v>50.81070689331764</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>26.77084881751448</v>
+        <v>26.41300094005257</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>1.216688146123627</v>
+        <v>0.651438836790813</v>
       </c>
       <c r="K87" s="2" t="n">
         <v>0</v>
@@ -5075,31 +5075,31 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>-0.4246602570764649</v>
+        <v>0.0605320740447153</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>6792</v>
+        <v>6584</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>詠業</t>
+          <t>南俊國際</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>334.0725170062251</v>
+        <v>341.4199016504267</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>58.5</v>
+        <v>541</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,13 +5110,13 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>46.97178687783853</v>
+        <v>43.44683479983154</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>26.25062875599392</v>
+        <v>19.01305257514808</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>1.133430258433967</v>
+        <v>2.247591968666175</v>
       </c>
       <c r="K88" s="2" t="n">
         <v>0</v>
@@ -5128,31 +5128,31 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>-0.0926879770245872</v>
+        <v>-2.791248252531744</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>6763</v>
+        <v>6494</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>綠界科技</t>
+          <t>九齊</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>328.388072970229</v>
+        <v>338.9419479872615</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>41.1</v>
+        <v>52.9</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,13 +5163,13 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>44.96033935518869</v>
+        <v>53.21813010726287</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>16.44076448021465</v>
+        <v>10.82376528808867</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>1.196923711372626</v>
+        <v>0.8848343262874399</v>
       </c>
       <c r="K89" s="2" t="n">
         <v>0</v>
@@ -5181,31 +5181,31 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>0.0605849232350306</v>
+        <v>0.3402770853761661</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>6504</v>
+        <v>6741</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>南六</t>
+          <t>91APP*-KY</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>321.9328279720825</v>
+        <v>336.5454925231704</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>37.05</v>
+        <v>54.9</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,13 +5216,13 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>47.58765075820141</v>
+        <v>34.98015773294421</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>26.46313492029098</v>
+        <v>26.77084875445967</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.9210755026784136</v>
+        <v>1.216688146123627</v>
       </c>
       <c r="K90" s="2" t="n">
         <v>0</v>
@@ -5234,31 +5234,31 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>0.0547581921245598</v>
+        <v>-0.4246602571877397</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>6606</v>
+        <v>6792</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>建德工業</t>
+          <t>詠業</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>309.4384856426571</v>
+        <v>334.072517006225</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>24.85</v>
+        <v>58.5</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,16 +5269,16 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>42.19724555929754</v>
+        <v>46.97178660239013</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>27.14078798624167</v>
+        <v>26.25062885573628</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>1.467403520567883</v>
+        <v>1.133430258433967</v>
       </c>
       <c r="K91" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L91" s="2" t="n">
         <v>0</v>
@@ -5287,31 +5287,31 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>-0.004276982378854</v>
+        <v>-0.0926879763569611</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>6581</v>
+        <v>6761</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>鋼聯</t>
+          <t>穩得</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>307.5557135985353</v>
+        <v>332.4422696944141</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>108</v>
+        <v>169.5</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,13 +5322,13 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>41.92330342666321</v>
+        <v>50.66062119647713</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>14.53015843151754</v>
+        <v>15.87165260825126</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.7166123778501629</v>
+        <v>1.277745377065502</v>
       </c>
       <c r="K92" s="2" t="n">
         <v>0</v>
@@ -5340,31 +5340,31 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>-0.2506480707544641</v>
+        <v>0.4111072867694498</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>6560</v>
+        <v>6763</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>欣普羅</t>
+          <t>綠界科技</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>303.1268386003831</v>
+        <v>328.3880729702199</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>31.2</v>
+        <v>41.1</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,13 +5375,13 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>47.33697503706583</v>
+        <v>44.96033949243938</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>11.13300047191511</v>
+        <v>16.44076447720476</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.942585520472676</v>
+        <v>1.196923711372626</v>
       </c>
       <c r="K93" s="2" t="n">
         <v>0</v>
@@ -5393,31 +5393,31 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>-0.1539273175278041</v>
+        <v>0.0605849231905233</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>6570</v>
+        <v>6498</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>維田</t>
+          <t>久禾光</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>300.3024943874559</v>
+        <v>324.5192435067038</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>47.45</v>
+        <v>69.8</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,13 +5428,13 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>41.40930133862557</v>
+        <v>49.63177323728259</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>22.08389012619141</v>
+        <v>14.21097237616251</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>0.5731004598343277</v>
+        <v>0.6881932067319685</v>
       </c>
       <c r="K94" s="2" t="n">
         <v>0</v>
@@ -5446,31 +5446,31 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>0.2167534066640737</v>
+        <v>0.5946815169450699</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>6592</v>
+        <v>6504</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>和潤企業</t>
+          <t>南六</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>297.5862496449493</v>
+        <v>321.9328279720825</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>55.4</v>
+        <v>37.05</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,16 +5481,16 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>18.51340906798727</v>
+        <v>47.58765097262936</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>31.66488723141022</v>
+        <v>26.46313506539905</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>2.582062336255115</v>
+        <v>0.9210755026784136</v>
       </c>
       <c r="K95" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L95" s="2" t="n">
         <v>0</v>
@@ -5499,31 +5499,31 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>-0.3236201062937625</v>
+        <v>0.054758191768491</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>6598</v>
+        <v>6807</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>ABC-KY</t>
+          <t>峰源-KY</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>296.6424071159427</v>
+        <v>319.9482036409438</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>26.8</v>
+        <v>32.05</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,13 +5534,13 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>43.77536850078536</v>
+        <v>50.9177455152098</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>12.82814435855909</v>
+        <v>12.24534773138725</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0.9517851745360428</v>
+        <v>0.8516087144712162</v>
       </c>
       <c r="K96" s="2" t="n">
         <v>0</v>
@@ -5552,31 +5552,31 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>-0.1032079940577516</v>
+        <v>0.5622689328336592</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>6803</v>
+        <v>6606</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>崑鼎</t>
+          <t>建德工業</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>295.4708296216066</v>
+        <v>309.4384856426571</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>265.5</v>
+        <v>24.85</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,16 +5587,16 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>35.64365225493619</v>
+        <v>42.19724551578423</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>21.1053495535317</v>
+        <v>27.14078798624167</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>2.240798717971063</v>
+        <v>1.467403520567883</v>
       </c>
       <c r="K97" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L97" s="2" t="n">
         <v>0</v>
@@ -5605,31 +5605,31 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>-0.0626168148013774</v>
+        <v>-0.0042769823677268</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>6585</v>
+        <v>6581</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>鼎基</t>
+          <t>鋼聯</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>294.9898075645722</v>
+        <v>307.5557135985352</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>103.5</v>
+        <v>108</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,13 +5640,13 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>39.35401078372473</v>
+        <v>41.92330369920173</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>32.87696843179618</v>
+        <v>14.5301587340727</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>0.727378957782631</v>
+        <v>0.7166123778501629</v>
       </c>
       <c r="K98" s="2" t="n">
         <v>0</v>
@@ -5658,31 +5658,31 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>0.2760415224558943</v>
+        <v>-0.2506480709769969</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>6753</v>
+        <v>6560</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>龍德造船</t>
+          <t>欣普羅</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>288.9743866661099</v>
+        <v>303.1268386003833</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>131</v>
+        <v>31.2</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,13 +5693,13 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>40.78615381347864</v>
+        <v>47.33697501323972</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>10.17851183730441</v>
+        <v>11.13300055336707</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>0.8713361423502883</v>
+        <v>0.942585520472676</v>
       </c>
       <c r="K99" s="2" t="n">
         <v>0</v>
@@ -5711,31 +5711,31 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>0.0552060213395344</v>
+        <v>-0.1539273173831504</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>6796</v>
+        <v>6570</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>晉弘</t>
+          <t>維田</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>288.1727519046976</v>
+        <v>300.3024943874559</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>57</v>
+        <v>47.45</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,13 +5746,13 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>57.45254144652111</v>
+        <v>41.40930135036279</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>23.56677666346512</v>
+        <v>22.08389009050574</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.9723730460623458</v>
+        <v>0.5731004598343277</v>
       </c>
       <c r="K100" s="2" t="n">
         <v>0</v>
@@ -5764,31 +5764,31 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>0.8003713584435928</v>
+        <v>0.2167534067419601</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>6829</v>
+        <v>6598</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>千附精密</t>
+          <t>ABC-KY</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>266.28548283462</v>
+        <v>296.6424071159427</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>206</v>
+        <v>26.8</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,13 +5799,13 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>43.56104770547404</v>
+        <v>43.77536850078536</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>11.57211873037704</v>
+        <v>12.82814427501187</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>0.5000243875959967</v>
+        <v>0.9517851745360428</v>
       </c>
       <c r="K101" s="2" t="n">
         <v>0</v>
@@ -5817,31 +5817,31 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>-1.956134684866792</v>
+        <v>-0.1032079940577516</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>6550</v>
+        <v>6803</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>北極星藥業-KY</t>
+          <t>崑鼎</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>251.6895621757138</v>
+        <v>295.4708296216066</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>16.2</v>
+        <v>265.5</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5852,13 +5852,13 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>70.22089235414047</v>
+        <v>35.64365215389793</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>29.93085862076828</v>
+        <v>21.10534961866659</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>0.6848968793338485</v>
+        <v>2.240798717971063</v>
       </c>
       <c r="K102" s="2" t="n">
         <v>0</v>
@@ -5870,31 +5870,31 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>0.797378906320618</v>
+        <v>-0.06261681457880899</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, adx_trending, above_ichimoku_cloud</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>6597</v>
+        <v>6585</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>立誠</t>
+          <t>鼎基</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>251.585121063763</v>
+        <v>294.9898075645722</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>64.90000000000001</v>
+        <v>103.5</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,13 +5905,13 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>51.73668398848905</v>
+        <v>39.35401084247752</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>6.291778955548449</v>
+        <v>32.87696844320824</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>0.7394463349581533</v>
+        <v>0.727378957782631</v>
       </c>
       <c r="K103" s="2" t="n">
         <v>0</v>
@@ -5923,31 +5923,31 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>1.203182288399889</v>
+        <v>0.2760415225004111</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>6614</v>
+        <v>6515</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>資拓宏宇</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>247.231283710148</v>
+        <v>290.1691603220797</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>35.3</v>
+        <v>6205</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,16 +5958,16 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>41.50134913771311</v>
+        <v>48.25481037709259</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>18.123725378941</v>
+        <v>11.60525668273473</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>2.447632695239129</v>
+        <v>0.92403387571079</v>
       </c>
       <c r="K104" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L104" s="2" t="n">
         <v>0</v>
@@ -5976,31 +5976,31 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>0.0200181911774411</v>
+        <v>-12.43129878068188</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, liquidity_ok, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>6823</v>
+        <v>6753</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>濾能</t>
+          <t>龍德造船</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>244.789756471223</v>
+        <v>288.9743866661099</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>60.8</v>
+        <v>131</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6011,13 +6011,13 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>49.50420890263133</v>
+        <v>40.78615333510579</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>22.92984123684548</v>
+        <v>10.17851181616877</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>0.6880264723349402</v>
+        <v>0.8713361423502883</v>
       </c>
       <c r="K105" s="2" t="n">
         <v>0</v>
@@ -6029,31 +6029,31 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>0.3061961816090128</v>
+        <v>0.055206022786066</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>6556</v>
+        <v>6829</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>勝品</t>
+          <t>千附精密</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>243.7156285168064</v>
+        <v>266.2854828346201</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>60.9</v>
+        <v>206</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -6064,16 +6064,16 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>44.64350371869224</v>
+        <v>43.56104764511008</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>9.06859899494836</v>
+        <v>11.5721187543551</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>1.565394116140545</v>
+        <v>0.5000243875959967</v>
       </c>
       <c r="K106" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L106" s="2" t="n">
         <v>0</v>
@@ -6082,31 +6082,31 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>0.0627882506946659</v>
+        <v>-1.956134683754083</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>6776</v>
+        <v>6597</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>展碁國際</t>
+          <t>立誠</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>234.8283195637661</v>
+        <v>251.5851210637629</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>52.4</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -6117,13 +6117,13 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>46.58388964301507</v>
+        <v>51.73668398662998</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>13.91323580972067</v>
+        <v>6.291778879496313</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>0.8446110696493955</v>
+        <v>0.7394463349581533</v>
       </c>
       <c r="K107" s="2" t="n">
         <v>0</v>
@@ -6135,31 +6135,31 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>0.1171856823598863</v>
+        <v>1.203182287465205</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>6568</v>
+        <v>6614</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>宏觀</t>
+          <t>資拓宏宇</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>232.4303719775078</v>
+        <v>247.231283710148</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>137.5</v>
+        <v>35.3</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -6170,13 +6170,13 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>48.62278099813816</v>
+        <v>41.50134952266797</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>19.47940493146311</v>
+        <v>18.12372544171096</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>1.390936628290122</v>
+        <v>2.447632695239129</v>
       </c>
       <c r="K108" s="2" t="n">
         <v>0</v>
@@ -6188,31 +6188,31 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>0.1346259691178699</v>
+        <v>0.0200181909548989</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>6477</v>
+        <v>6823</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>安集</t>
+          <t>濾能</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>232.3547017013064</v>
+        <v>244.7897564712232</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>34.05</v>
+        <v>60.8</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6223,13 +6223,13 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>45.794006061472</v>
+        <v>49.50420873165342</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>18.86706018904453</v>
+        <v>22.92984145229771</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>0.6181607751847994</v>
+        <v>0.6880264723349402</v>
       </c>
       <c r="K109" s="2" t="n">
         <v>0</v>
@@ -6241,31 +6241,31 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>0.06445717156136919</v>
+        <v>0.3061961828107401</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>6670</v>
+        <v>6556</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>復盛應用</t>
+          <t>勝品</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>222.6333195381617</v>
+        <v>243.7156285168064</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>270</v>
+        <v>60.9</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6276,16 +6276,16 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>46.41672866629789</v>
+        <v>44.64350368330649</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>18.79403725489587</v>
+        <v>9.06859908780914</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>0.645981025419144</v>
+        <v>1.565394116140545</v>
       </c>
       <c r="K110" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L110" s="2" t="n">
         <v>0</v>
@@ -6294,31 +6294,31 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>-0.7178737588232849</v>
+        <v>0.0627882504053696</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>6761</v>
+        <v>6605</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>穩得</t>
+          <t>帝寶</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>217.4422696944141</v>
+        <v>235.5314049099906</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>169.5</v>
+        <v>135.5</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6329,13 +6329,13 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>50.66062155303653</v>
+        <v>43.61920339551089</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>15.87165259801503</v>
+        <v>12.38836697448608</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>1.277745377065502</v>
+        <v>0.8222340728556957</v>
       </c>
       <c r="K111" s="2" t="n">
         <v>0</v>
@@ -6347,31 +6347,31 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>0.4111072845440073</v>
+        <v>-0.2249051512455985</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>6657</v>
+        <v>6776</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>華安</t>
+          <t>展碁國際</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>213.3610733002872</v>
+        <v>234.8283195637658</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>33</v>
+        <v>52.4</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6382,16 +6382,16 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>51.65930865124076</v>
+        <v>46.58388911206106</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>19.60723403032077</v>
+        <v>13.91323599041605</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>0.3881097120503217</v>
+        <v>0.8446110696493955</v>
       </c>
       <c r="K112" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L112" s="2" t="n">
         <v>0</v>
@@ -6400,31 +6400,31 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>-0.144187521311371</v>
+        <v>0.1171856826491855</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>6790</v>
+        <v>6568</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>永豐實</t>
+          <t>宏觀</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>210.2518643093043</v>
+        <v>232.4303719775078</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>37.25</v>
+        <v>137.5</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -6435,13 +6435,13 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>32.99490677051925</v>
+        <v>48.62278099813816</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>15.91772574347132</v>
+        <v>19.47940488394553</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>1.521160837059129</v>
+        <v>1.390936628290122</v>
       </c>
       <c r="K113" s="2" t="n">
         <v>0</v>
@@ -6453,31 +6453,31 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>-0.0245825752729782</v>
+        <v>0.1346259695629483</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>6498</v>
+        <v>6477</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>久禾光</t>
+          <t>安集</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>209.5192435067038</v>
+        <v>232.3547017013064</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>69.8</v>
+        <v>34.05</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -6488,13 +6488,13 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>49.63177292802881</v>
+        <v>45.79400588358741</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>14.21097215018458</v>
+        <v>18.86706000448098</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>0.6881932067319685</v>
+        <v>0.6181607751847994</v>
       </c>
       <c r="K114" s="2" t="n">
         <v>0</v>
@@ -6506,7 +6506,7 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>0.5946815164999895</v>
+        <v>0.0644571719174368</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
@@ -6516,21 +6516,21 @@
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>6605</v>
+        <v>6670</v>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>帝寶</t>
+          <t>復盛應用</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
         <v/>
       </c>
       <c r="D115" s="2" t="n">
-        <v>175.5314049099906</v>
+        <v>222.6333195381616</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>135.5</v>
+        <v>270</v>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
@@ -6541,49 +6541,49 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>43.61920325060054</v>
+        <v>46.41672866629789</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>12.38836694981795</v>
+        <v>18.79403728766838</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>0.8222340728556957</v>
+        <v>0.645981025419144</v>
       </c>
       <c r="K115" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L115" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M115" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>-0.2249051505779749</v>
+        <v>-0.7178737590458354</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>6757</v>
+        <v>6657</v>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>台灣虎航-創</t>
+          <t>華安</t>
         </is>
       </c>
       <c r="C116" s="2" t="n">
         <v/>
       </c>
       <c r="D116" s="2" t="n">
-        <v>169.5177347427176</v>
+        <v>213.3610733002872</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
@@ -6594,16 +6594,16 @@
         <v>0</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>38.25985913951367</v>
+        <v>51.65930875030142</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>16.12096404155943</v>
+        <v>19.60723399715871</v>
       </c>
       <c r="J116" s="2" t="n">
-        <v>0.8784857720054714</v>
+        <v>0.3881097120503217</v>
       </c>
       <c r="K116" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L116" s="2" t="n">
         <v>0</v>
@@ -6612,31 +6612,31 @@
         <v>-1</v>
       </c>
       <c r="N116" s="2" t="n">
-        <v>-0.0024723046316142</v>
+        <v>-0.144187521311371</v>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>6698</v>
+        <v>6790</v>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>旭暉應材</t>
+          <t>永豐實</t>
         </is>
       </c>
       <c r="C117" s="2" t="n">
         <v/>
       </c>
       <c r="D117" s="2" t="n">
-        <v>163.8747781177247</v>
+        <v>210.2518643093043</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>31.35</v>
+        <v>37.25</v>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
@@ -6647,13 +6647,13 @@
         <v>0</v>
       </c>
       <c r="H117" s="2" t="n">
-        <v>44.86322190320081</v>
+        <v>32.99490663269185</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>12.53826143856087</v>
+        <v>15.9177257593311</v>
       </c>
       <c r="J117" s="2" t="n">
-        <v>1.139271117586567</v>
+        <v>1.521160837059129</v>
       </c>
       <c r="K117" s="2" t="n">
         <v>0</v>
@@ -6665,31 +6665,31 @@
         <v>-1</v>
       </c>
       <c r="N117" s="2" t="n">
-        <v>0.0611471852225746</v>
+        <v>-0.02458257525072</v>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>6546</v>
+        <v>6757</v>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>正基</t>
+          <t>台灣虎航-創</t>
         </is>
       </c>
       <c r="C118" s="2" t="n">
         <v/>
       </c>
       <c r="D118" s="2" t="n">
-        <v>151.9390629761908</v>
+        <v>169.5177347427176</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>60.8</v>
+        <v>53</v>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
@@ -6700,16 +6700,16 @@
         <v>0</v>
       </c>
       <c r="H118" s="2" t="n">
-        <v>51.6057460281251</v>
+        <v>38.25985922928402</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>15.73468103761913</v>
+        <v>16.12096393320907</v>
       </c>
       <c r="J118" s="2" t="n">
-        <v>0.6383256270127937</v>
+        <v>0.8784857720054714</v>
       </c>
       <c r="K118" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L118" s="2" t="n">
         <v>0</v>
@@ -6718,7 +6718,7 @@
         <v>-1</v>
       </c>
       <c r="N118" s="2" t="n">
-        <v>0.1744531282874432</v>
+        <v>-0.0024723048319035</v>
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
@@ -6728,21 +6728,21 @@
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>6624</v>
+        <v>6698</v>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>萬年清</t>
+          <t>旭暉應材</t>
         </is>
       </c>
       <c r="C119" s="2" t="n">
         <v/>
       </c>
       <c r="D119" s="2" t="n">
-        <v>143.7001253518232</v>
+        <v>163.8747781177238</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>39.5</v>
+        <v>31.35</v>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
@@ -6753,13 +6753,13 @@
         <v>0</v>
       </c>
       <c r="H119" s="2" t="n">
-        <v>52.70581491987363</v>
+        <v>44.86322167940643</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>5.468432853813363</v>
+        <v>12.53826150585743</v>
       </c>
       <c r="J119" s="2" t="n">
-        <v>0.1593090951150865</v>
+        <v>1.139271117586567</v>
       </c>
       <c r="K119" s="2" t="n">
         <v>0</v>
@@ -6771,31 +6771,31 @@
         <v>-1</v>
       </c>
       <c r="N119" s="2" t="n">
-        <v>0.2454512963045344</v>
+        <v>0.0611471855675162</v>
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>6720</v>
+        <v>6546</v>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>久昌</t>
+          <t>正基</t>
         </is>
       </c>
       <c r="C120" s="2" t="n">
         <v/>
       </c>
       <c r="D120" s="2" t="n">
-        <v>134.4468385026146</v>
+        <v>151.9390629761909</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>124.5</v>
+        <v>60.8</v>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
@@ -6806,16 +6806,16 @@
         <v>0</v>
       </c>
       <c r="H120" s="2" t="n">
-        <v>49.0068080153231</v>
+        <v>51.60574595004165</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>13.8449328237917</v>
+        <v>15.73468113777692</v>
       </c>
       <c r="J120" s="2" t="n">
-        <v>0.1757457289026095</v>
+        <v>0.6383256270127937</v>
       </c>
       <c r="K120" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L120" s="2" t="n">
         <v>0</v>
@@ -6824,7 +6824,7 @@
         <v>-1</v>
       </c>
       <c r="N120" s="2" t="n">
-        <v>0.9117917025859184</v>
+        <v>0.1744531286657785</v>
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
@@ -6834,21 +6834,21 @@
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>6754</v>
+        <v>6624</v>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>匯僑設計</t>
+          <t>萬年清</t>
         </is>
       </c>
       <c r="C121" s="2" t="n">
         <v/>
       </c>
       <c r="D121" s="2" t="n">
-        <v>130.8341998184507</v>
+        <v>143.7001253518232</v>
       </c>
       <c r="E121" s="2" t="n">
-        <v>41</v>
+        <v>39.5</v>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
@@ -6859,13 +6859,13 @@
         <v>0</v>
       </c>
       <c r="H121" s="2" t="n">
-        <v>41.42216038181919</v>
+        <v>52.7058149161813</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>11.08598353835953</v>
+        <v>5.468432853662638</v>
       </c>
       <c r="J121" s="2" t="n">
-        <v>4.283419981845074</v>
+        <v>0.1593090951150865</v>
       </c>
       <c r="K121" s="2" t="n">
         <v>0</v>
@@ -6877,31 +6877,31 @@
         <v>-1</v>
       </c>
       <c r="N121" s="2" t="n">
-        <v>-0.0683662264174351</v>
+        <v>0.2454512963045344</v>
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>6515</v>
+        <v>6720</v>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>久昌</t>
         </is>
       </c>
       <c r="C122" s="2" t="n">
         <v/>
       </c>
       <c r="D122" s="2" t="n">
-        <v>130.1691603220793</v>
+        <v>134.446838502614</v>
       </c>
       <c r="E122" s="2" t="n">
-        <v>6205</v>
+        <v>124.5</v>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
@@ -6912,16 +6912,16 @@
         <v>0</v>
       </c>
       <c r="H122" s="2" t="n">
-        <v>48.25481037090881</v>
+        <v>49.00680803277892</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>11.60525662492984</v>
+        <v>13.84493283390513</v>
       </c>
       <c r="J122" s="2" t="n">
-        <v>0.92403387571079</v>
+        <v>0.1757457289026095</v>
       </c>
       <c r="K122" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L122" s="2" t="n">
         <v>0</v>
@@ -6930,31 +6930,31 @@
         <v>-1</v>
       </c>
       <c r="N122" s="2" t="n">
-        <v>-12.43129877623159</v>
+        <v>0.9117917018070436</v>
       </c>
       <c r="O122" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
-        <v>6582</v>
+        <v>6754</v>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>申豐</t>
+          <t>匯僑設計</t>
         </is>
       </c>
       <c r="C123" s="2" t="n">
         <v/>
       </c>
       <c r="D123" s="2" t="n">
-        <v>123.3278195525631</v>
+        <v>130.8341998184507</v>
       </c>
       <c r="E123" s="2" t="n">
-        <v>31.35</v>
+        <v>41</v>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
@@ -6965,13 +6965,13 @@
         <v>0</v>
       </c>
       <c r="H123" s="2" t="n">
-        <v>47.87548240114857</v>
+        <v>41.42216043810919</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>12.42996386487065</v>
+        <v>11.08598348744739</v>
       </c>
       <c r="J123" s="2" t="n">
-        <v>0.605369972722807</v>
+        <v>4.283419981845074</v>
       </c>
       <c r="K123" s="2" t="n">
         <v>0</v>
@@ -6983,31 +6983,31 @@
         <v>-1</v>
       </c>
       <c r="N123" s="2" t="n">
-        <v>0.0318889541264826</v>
+        <v>-0.06836622666223501</v>
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>volume_break, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
-        <v>6807</v>
+        <v>6582</v>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>峰源-KY</t>
+          <t>申豐</t>
         </is>
       </c>
       <c r="C124" s="2" t="n">
         <v/>
       </c>
       <c r="D124" s="2" t="n">
-        <v>119.9482036409439</v>
+        <v>123.3278195525626</v>
       </c>
       <c r="E124" s="2" t="n">
-        <v>32.05</v>
+        <v>31.35</v>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
@@ -7018,13 +7018,13 @@
         <v>0</v>
       </c>
       <c r="H124" s="2" t="n">
-        <v>50.91774550774677</v>
+        <v>47.87548242667012</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>12.24534775378266</v>
+        <v>12.42996386929022</v>
       </c>
       <c r="J124" s="2" t="n">
-        <v>0.8516087144712162</v>
+        <v>0.605369972722807</v>
       </c>
       <c r="K124" s="2" t="n">
         <v>0</v>
@@ -7036,11 +7036,11 @@
         <v>-1</v>
       </c>
       <c r="N124" s="2" t="n">
-        <v>0.5622689329115449</v>
+        <v>0.0318889541042285</v>
       </c>
       <c r="O124" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
@@ -7057,7 +7057,7 @@
         <v/>
       </c>
       <c r="D125" s="2" t="n">
-        <v>93.9067365475464</v>
+        <v>93.90673654754512</v>
       </c>
       <c r="E125" s="2" t="n">
         <v>73.7</v>
@@ -7071,7 +7071,7 @@
         <v>0</v>
       </c>
       <c r="H125" s="2" t="n">
-        <v>39.14896371929758</v>
+        <v>39.1489641364157</v>
       </c>
       <c r="I125" s="2" t="n">
         <v>12.87872036839565</v>
@@ -7089,7 +7089,7 @@
         <v>-1</v>
       </c>
       <c r="N125" s="2" t="n">
-        <v>0.0231711557429422</v>
+        <v>0.0231711557206866</v>
       </c>
       <c r="O125" s="2" t="inlineStr">
         <is>
